--- a/example_analysis/4_go_enrichment/down-regulated_306/results/orthogather_GOenrichment-results_fg306_evidence-all_2026-09-14.xlsx
+++ b/example_analysis/4_go_enrichment/down-regulated_306/results/orthogather_GOenrichment-results_fg306_evidence-all_2026-09-14.xlsx
@@ -298,7 +298,7 @@
     <t>2.1.0</t>
   </si>
   <si>
-    <t>2026-09-13T23:00:14.803866+00:00</t>
+    <t>2026-09-13T23:03:10.876558+00:00</t>
   </si>
   <si>
     <t>UniProt (rest.uniprot.org)</t>
@@ -328,7 +328,7 @@
     <t>http://purl.obolibrary.org/obo/go/releases/2026-07-26/extensions/go-plus.ofn</t>
   </si>
   <si>
-    <t>2026-09-13T22:59:52.530909+00:00</t>
+    <t>2026-09-13T23:02:49.348340+00:00</t>
   </si>
   <si>
     <t>EBI GOA proteomes (ftp.ebi.ac.uk/pub/databases/GO/goa/proteomes)</t>
